--- a/Excel files/Unit_Test_Plan InfySpringboard.xlsx
+++ b/Excel files/Unit_Test_Plan InfySpringboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://infosystechnologies-my.sharepoint.com/personal/kamaljeet_kaur01_ad_infosys_com1/Documents/Infosys/CC/Events/Oct 2021 - Mar 2022/CC2.0/Internship/Jan-Apr 2022/Artifacts/internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="8_{3B9D4FEA-5A3F-460B-9A40-165575443B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCE2D018-2102-4B0C-A658-30D70148EE13}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="8_{3B9D4FEA-5A3F-460B-9A40-165575443B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87E56E8C-B610-4951-AC89-B29A790BE24D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="67">
   <si>
     <t>Sl: No:</t>
   </si>
@@ -201,13 +201,49 @@
   </si>
   <si>
     <t>Markdown ticket file is successfully created</t>
+  </si>
+  <si>
+    <t>API Workflow Execution</t>
+  </si>
+  <si>
+    <t>Run test_api.py for workflow execution</t>
+  </si>
+  <si>
+    <t>Verify the API triggers the agent workflow.</t>
+  </si>
+  <si>
+    <t>Workflow response returned.</t>
+  </si>
+  <si>
+    <t>Incident Ticket Retrieval</t>
+  </si>
+  <si>
+    <t>Test GET/tickets</t>
+  </si>
+  <si>
+    <t>Verify incident tickets are retrieved successfully.</t>
+  </si>
+  <si>
+    <t>Ticket details returned.</t>
+  </si>
+  <si>
+    <t>Health Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test GET/health</t>
+  </si>
+  <si>
+    <t>Verify API and dependency health.</t>
+  </si>
+  <si>
+    <t>Health status returned.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -215,7 +251,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color indexed="56"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -223,33 +259,39 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF1F2328"/>
+      <color theme="1"/>
       <name val="-Apple-System"/>
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Ui-Monospace"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="-Apple-System"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Ui-Monospace"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
+      <color theme="1"/>
+      <name val="Google Sans Text"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -266,7 +308,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -289,74 +331,29 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -671,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -692,232 +689,292 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15">
-      <c r="A10" s="13">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="7" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12" t="s">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="12">
+      <c r="A12" s="8">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="8" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
